--- a/internships.xlsx
+++ b/internships.xlsx
@@ -1330,7 +1330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1825,7 +1825,6 @@
       <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>0.8</v>
       </c>
@@ -1882,7 +1881,6 @@
       <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>0.11</v>
       </c>
@@ -2014,6 +2012,303 @@
         </is>
       </c>
       <c r="O11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>RUN-20261018-170455</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-10-18 17:04:55</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apify-LinkedIn</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://api.apify.com/v2/acts//run-sync-get-dataset-items?token=[REDACTED]&amp;timeout=120&amp;memory=1024&amp;limit=100</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>RUN-20261018-170455</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-10-18 17:04:55</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Internshala</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>34</v>
+      </c>
+      <c r="F13" t="n">
+        <v>14</v>
+      </c>
+      <c r="G13" t="n">
+        <v>26</v>
+      </c>
+      <c r="H13" t="n">
+        <v>26</v>
+      </c>
+      <c r="I13" t="n">
+        <v>8</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>RUN-20261018-170455</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-10-18 17:04:55</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>TimesJobs</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Zero Results</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>RUN-20261018-170455</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-10-18 17:04:55</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Adzuna</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>ADZUNA credentials not configured</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>RUN-20261018-170455</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-10-18 17:04:55</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>JSearch</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>RAPIDAPI_KEY not configured</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>

--- a/internships.xlsx
+++ b/internships.xlsx
@@ -1330,7 +1330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2120,7 +2120,6 @@
       <c r="K13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>2.06</v>
       </c>
@@ -2177,7 +2176,6 @@
       <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>0.47</v>
       </c>
@@ -2309,6 +2307,303 @@
         </is>
       </c>
       <c r="O16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>RUN-20261019-132850</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:28:50</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apify-LinkedIn</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://api.apify.com/v2/acts//run-sync-get-dataset-items?token=[REDACTED]&amp;timeout=120&amp;memory=1024&amp;limit=100</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>RUN-20261019-132850</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:28:50</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Internshala</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>35</v>
+      </c>
+      <c r="F18" t="n">
+        <v>14</v>
+      </c>
+      <c r="G18" t="n">
+        <v>27</v>
+      </c>
+      <c r="H18" t="n">
+        <v>27</v>
+      </c>
+      <c r="I18" t="n">
+        <v>8</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>RUN-20261019-132850</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:28:50</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>TimesJobs</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Zero Results</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>RUN-20261019-132850</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:28:50</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Adzuna</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>ADZUNA credentials not configured</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>RUN-20261019-132850</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:28:50</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>JSearch</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>RAPIDAPI_KEY not configured</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>

--- a/internships.xlsx
+++ b/internships.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:U11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -448,7 +448,7 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="40" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
@@ -1296,6 +1296,191 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ISHALA-510328074e7fefba</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>AI Engineer Intern</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Enlight Lab</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Work from home</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0-1 yrs</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Not Disclosed</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1. Build AI agents that can reason, take actions, and interact with tools (APIs, databases, wo</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Fresher / Entry-Level</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Internshala</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>https://internshala.com/internship/detail/work-from-home-ai-agent-development-internship-at-enlight-lab1792132502</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>https://internshala.com/internship/detail/work-from-home-ai-agent-development-internship-at-enlight-lab1792132502</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>2026-10-20 13:19:14</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>80</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>'+20 pts: Remote / WFH eligible; +30 pts: Title matches target role keywords (ai engineer); +20 pts: Explicit internship/fresher designation in title; +10 pts: Legitimate application link present</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ISHALA-8f6b71f8a0d29464</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Software Development Engineer (SDE) – AI &amp; Machine Learning</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Street Surge Technologies</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Gurgaon</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0-1 yrs</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Not Disclosed</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1. Design, build, and maintain full-stack features using Java or Python backends and React use</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>java, react, python</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Fresher / Entry-Level</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Internshala</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>https://internshala.com/internship/detail/software-development-engineer-sde--ai-machine-learning-internship-in-gurgaon-at-street-surge-technologies1792396187</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>https://internshala.com/internship/detail/software-development-engineer-sde--ai-machine-learning-internship-in-gurgaon-at-street-surge-technologies1792396187</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>2026-10-20 13:19:14</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>69</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>'+20 pts: Delhi-NCR location; +30 pts: Title matches target role keywords (software, machine learning); +9 pts: Relevant technical skills found (python, react, java); +10 pts: Legitimate application link present</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
         <is>
           <t>Not Applied</t>
         </is>
@@ -1319,6 +1504,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1330,7 +1519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2415,7 +2604,6 @@
       <c r="K18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
         <v>2.11</v>
       </c>
@@ -2472,7 +2660,6 @@
       <c r="K19" t="n">
         <v>0</v>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
         <v>0.47</v>
       </c>
@@ -2604,6 +2791,301 @@
         </is>
       </c>
       <c r="O21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>RUN-20261020-131857</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-10-20 13:18:57</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apify-LinkedIn</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://api.apify.com/v2/acts//run-sync-get-dataset-items?token=[REDACTED]&amp;timeout=120&amp;memory=1024&amp;limit=100</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>RUN-20261020-131857</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-10-20 13:18:57</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Internshala</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>34</v>
+      </c>
+      <c r="F23" t="n">
+        <v>13</v>
+      </c>
+      <c r="G23" t="n">
+        <v>24</v>
+      </c>
+      <c r="H23" t="n">
+        <v>26</v>
+      </c>
+      <c r="I23" t="n">
+        <v>8</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>RUN-20261020-131857</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-10-20 13:18:57</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>TimesJobs</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Zero Results</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>RUN-20261020-131857</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-10-20 13:18:57</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Adzuna</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>ADZUNA credentials not configured</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>RUN-20261020-131857</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-10-20 13:18:57</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>JSearch</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>RAPIDAPI_KEY not configured</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2620,7 +3102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2971,6 +3453,90 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ISHALA-510328074e7fefba</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://internshala.com/internship/detail/work-from-home-ai-agent-development-internship-at-enlight-lab1792132502</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AI Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Enlight Lab</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Internshala</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-10-20 13:19:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ISHALA-8f6b71f8a0d29464</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>https://internshala.com/internship/detail/software-development-engineer-sde--ai-machine-learning-internship-in-gurgaon-at-street-surge-technologies1792396187</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Software Development Engineer (SDE) – AI &amp; Machine Learning</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Street Surge Technologies</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Internshala</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-10-20 13:19:17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2982,7 +3548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3313,6 +3879,90 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ISHALA-510328074e7fefba</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>AI Engineer Intern</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Enlight Lab</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Work from home</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://internshala.com/internship/detail/work-from-home-ai-agent-development-internship-at-enlight-lab1792132502</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ISHALA-8f6b71f8a0d29464</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Software Development Engineer (SDE) – AI &amp; Machine Learning</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Street Surge Technologies</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Gurgaon</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://internshala.com/internship/detail/software-development-engineer-sde--ai-machine-learning-internship-in-gurgaon-at-street-surge-technologies1792396187</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
@@ -3321,6 +3971,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/internships.xlsx
+++ b/internships.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U11"/>
+  <dimension ref="A1:U12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1486,6 +1486,103 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ISHALA-d04a7d6f48b23066</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>AI Product Developer - Python &amp; React (Remote)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AIVOA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Work from home</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0-1 yrs</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Not Disclosed</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1. Build backend APIs using Python and FastAPI.
+2. Develop frontend features using React.
+3.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>react, python</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Fresher / Entry-Level</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Internshala</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>https://internshala.com/internship/detail/work-from-home-ai-product-developer-python-react-remote-internship-at-aivoa1792558013</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>https://internshala.com/internship/detail/work-from-home-ai-product-developer-python-react-remote-internship-at-aivoa1792558013</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:22:59</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>66</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>'+20 pts: Remote / WFH eligible; +30 pts: Title matches target role keywords (python, developer); +6 pts: Relevant technical skills found (python, react); +10 pts: Legitimate application link present</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
@@ -1508,6 +1605,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1519,7 +1618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3091,6 +3190,301 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>RUN-20261021-132241</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:22:41</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Apify-LinkedIn</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://api.apify.com/v2/acts//run-sync-get-dataset-items?token=[REDACTED]&amp;timeout=120&amp;memory=1024&amp;limit=100</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>RUN-20261021-132241</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:22:41</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Internshala</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>35</v>
+      </c>
+      <c r="F28" t="n">
+        <v>14</v>
+      </c>
+      <c r="G28" t="n">
+        <v>24</v>
+      </c>
+      <c r="H28" t="n">
+        <v>25</v>
+      </c>
+      <c r="I28" t="n">
+        <v>10</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>RUN-20261021-132241</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:22:41</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>TimesJobs</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Zero Results</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>RUN-20261021-132241</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:22:41</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Adzuna</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>ADZUNA credentials not configured</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>RUN-20261021-132241</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:22:41</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>JSearch</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>RAPIDAPI_KEY not configured</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3102,7 +3496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3112,7 +3506,7 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -3534,6 +3928,48 @@
       <c r="H11" t="inlineStr">
         <is>
           <t>2026-10-20 13:19:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ISHALA-d04a7d6f48b23066</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://internshala.com/internship/detail/work-from-home-ai-product-developer-python-react-remote-internship-at-aivoa1792558013</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AI Product Developer - Python &amp; React (Remote)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AIVOA</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Internshala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:23:03</t>
         </is>
       </c>
     </row>
@@ -3548,7 +3984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3963,6 +4399,48 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ISHALA-d04a7d6f48b23066</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>AI Product Developer - Python &amp; React (Remote)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AIVOA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Work from home</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://internshala.com/internship/detail/work-from-home-ai-product-developer-python-react-remote-internship-at-aivoa1792558013</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
@@ -3973,6 +4451,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/internships.xlsx
+++ b/internships.xlsx
@@ -1618,7 +1618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:O36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3480,6 +3480,303 @@
         </is>
       </c>
       <c r="O31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>RUN-20261022-131858</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-10-22 13:18:58</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Apify-LinkedIn</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://api.apify.com/v2/acts//run-sync-get-dataset-items?token=[REDACTED]&amp;timeout=120&amp;memory=1024&amp;limit=100</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>RUN-20261022-131858</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-10-22 13:18:58</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Internshala</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>32</v>
+      </c>
+      <c r="F33" t="n">
+        <v>14</v>
+      </c>
+      <c r="G33" t="n">
+        <v>23</v>
+      </c>
+      <c r="H33" t="n">
+        <v>23</v>
+      </c>
+      <c r="I33" t="n">
+        <v>9</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>RUN-20261022-131858</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-10-22 13:18:58</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>TimesJobs</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Zero Results</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>RUN-20261022-131858</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-10-22 13:18:58</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Adzuna</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>ADZUNA credentials not configured</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>RUN-20261022-131858</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-10-22 13:18:58</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>JSearch</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>RAPIDAPI_KEY not configured</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>

--- a/internships.xlsx
+++ b/internships.xlsx
@@ -1618,7 +1618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O36"/>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3588,7 +3588,6 @@
       <c r="K33" t="n">
         <v>0</v>
       </c>
-      <c r="L33" t="inlineStr"/>
       <c r="M33" t="n">
         <v>2.05</v>
       </c>
@@ -3645,7 +3644,6 @@
       <c r="K34" t="n">
         <v>0</v>
       </c>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="n">
         <v>0.48</v>
       </c>
@@ -3777,6 +3775,303 @@
         </is>
       </c>
       <c r="O36" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>RUN-20261023-131744</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-10-23 13:17:44</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Apify-LinkedIn</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://api.apify.com/v2/acts//run-sync-get-dataset-items?token=[REDACTED]&amp;timeout=120&amp;memory=1024&amp;limit=100</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>RUN-20261023-131744</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-10-23 13:17:44</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Internshala</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>34</v>
+      </c>
+      <c r="F38" t="n">
+        <v>15</v>
+      </c>
+      <c r="G38" t="n">
+        <v>25</v>
+      </c>
+      <c r="H38" t="n">
+        <v>25</v>
+      </c>
+      <c r="I38" t="n">
+        <v>9</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>RUN-20261023-131744</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-10-23 13:17:44</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>TimesJobs</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Zero Results</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>RUN-20261023-131744</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-10-23 13:17:44</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Adzuna</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>ADZUNA credentials not configured</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>RUN-20261023-131744</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-10-23 13:17:44</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>JSearch</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>RAPIDAPI_KEY not configured</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>

--- a/internships.xlsx
+++ b/internships.xlsx
@@ -1618,7 +1618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3883,7 +3883,6 @@
       <c r="K38" t="n">
         <v>0</v>
       </c>
-      <c r="L38" t="inlineStr"/>
       <c r="M38" t="n">
         <v>0.79</v>
       </c>
@@ -3940,7 +3939,6 @@
       <c r="K39" t="n">
         <v>0</v>
       </c>
-      <c r="L39" t="inlineStr"/>
       <c r="M39" t="n">
         <v>0.42</v>
       </c>
@@ -4072,6 +4070,303 @@
         </is>
       </c>
       <c r="O41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>RUN-20261024-125958</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-10-24 12:59:58</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Apify-LinkedIn</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>404 Client Error: Not Found for url: https://api.apify.com/v2/acts//run-sync-get-dataset-items?token=[REDACTED]&amp;timeout=120&amp;memory=1024&amp;limit=100</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>RUN-20261024-125958</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-10-24 12:59:58</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Internshala</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>31</v>
+      </c>
+      <c r="F43" t="n">
+        <v>15</v>
+      </c>
+      <c r="G43" t="n">
+        <v>22</v>
+      </c>
+      <c r="H43" t="n">
+        <v>22</v>
+      </c>
+      <c r="I43" t="n">
+        <v>9</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>RUN-20261024-125958</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-10-24 12:59:58</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>TimesJobs</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Zero Results</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>RUN-20261024-125958</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-10-24 12:59:58</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Adzuna</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>ADZUNA credentials not configured</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>RUN-20261024-125958</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-10-24 12:59:58</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>JSearch</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>RAPIDAPI_KEY not configured</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
